--- a/docs/research/drone-winter-spreading/model.xlsx
+++ b/docs/research/drone-winter-spreading/model.xlsx
@@ -62,9 +62,11 @@
     <definedName name="liq_flight_min">'Параметры'!$C$52</definedName>
     <definedName name="liq_refill_min">'Параметры'!$C$53</definedName>
     <definedName name="liq_cycle_equiv_min">'Параметры'!$C$54</definedName>
-    <definedName name="drones_in_winter">'Параметры'!$C$56</definedName>
-    <definedName name="spreaders_owned">'Параметры'!$C$57</definedName>
-    <definedName name="season_one_time_other">'Параметры'!$C$58</definedName>
+    <definedName name="unified_tariff_per_ton">'Параметры'!$C$56</definedName>
+    <definedName name="min_order_t">'Параметры'!$C$57</definedName>
+    <definedName name="drones_in_winter">'Параметры'!$C$59</definedName>
+    <definedName name="spreaders_owned">'Параметры'!$C$60</definedName>
+    <definedName name="season_one_time_other">'Параметры'!$C$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -510,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1969,7 +1971,7 @@
       <c r="A55" s="2" t="n"/>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>СЕЗОН</t>
+          <t>ЕДИНЫЙ ТАРИФ (РЕШЕНИЕ ВЛАДЕЛЬЦА 30.10.2026)</t>
         </is>
       </c>
       <c r="C55" s="2" t="n"/>
@@ -1980,20 +1982,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>drones_in_winter</t>
+          <t>unified_tariff_per_ton</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Бортов в зимней работе</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>5</v>
+          <t>Единый тариф за тонну внесённого удобрения</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>1800000</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>сум/т</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2003,68 +2005,140 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Из 15 в парке.</t>
+          <t>Один тариф для любого гранулированного удобрения при нормах от 100 кг/га; округление целевого 1 778 000.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>min_order_t</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Минимальный заказ</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>РЕШЕНИЕ</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>За один выезд. Отсекает мелкие работы; 2 т = 10 га при 200 кг/га, выручка 3,6 млн сум.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>СЕЗОН</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>drones_in_winter</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Бортов в зимней работе</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>РЕШЕНИЕ</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Из 15 в парке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>spreaders_owned</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Разбрасывателей уже есть</t>
         </is>
       </c>
-      <c r="C57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="C60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>ФАКТ</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>Один тестовый бак.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>season_one_time_other</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Разовые расходы сезона (обучение, демо, оснастка загрузки)</t>
         </is>
       </c>
-      <c r="C58" s="6" t="n">
+      <c r="C61" s="6" t="n">
         <v>20000000</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>сум</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>ДОГАДКА</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>Жёлтые ячейки -- входы. Всё остальное в книге считается из них. Тип: ФАКТ -- с источником; ОЦЕНКА -- вывод из фактов; ДОГАДКА -- не проверено; РЕШЕНИЕ -- задаёт владелец.</t>
         </is>
@@ -13309,7 +13383,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Выручка по целевому тарифу</t>
+          <t>Выручка по единому тарифу за тонну</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -13318,11 +13392,11 @@
         </is>
       </c>
       <c r="C4" s="10">
-        <f>C3*'Расчёт'!D66</f>
+        <f>C3*'Расчёт'!D2/1000*unified_tariff_per_ton</f>
         <v/>
       </c>
       <c r="D4" s="10">
-        <f>D3*'Расчёт'!F66</f>
+        <f>D3*'Расчёт'!F2/1000*unified_tariff_per_ton</f>
         <v/>
       </c>
     </row>
@@ -13711,7 +13785,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>СТОРОНА ФЕРМЕРА: селитра 200 кг/га, тариф «за тонну» базы 250</t>
+          <t>СТОРОНА ФЕРМЕРА: селитра 200 кг/га, единый тариф за тонну</t>
         </is>
       </c>
     </row>
@@ -13750,7 +13824,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Услуга дрона: ставка за тонну x норма, не ниже минимума за гектар</t>
+          <t>Услуга дрона: единый тариф за тонну x норма</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -13759,7 +13833,7 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>MAX('Расчёт'!F80*10000/(swath_eff_m*speed_ms)/60*flow_kg_min/1000,'Расчёт'!F80*C17/1000)</f>
+        <f>unified_tariff_per_ton*C17/1000</f>
         <v/>
       </c>
     </row>
@@ -13877,7 +13951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -13888,7 +13962,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ТАРИФ ДЛЯ КП: ставка за тонну и минимум за гектар (из сценария «База 250», округление до 5 000 сум)</t>
+          <t>ТАРИФ ДЛЯ КП: единый тариф за тонну (решение владельца 30.10.2026)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -13897,7 +13971,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ставка за тонну внесённого удобрения</t>
+          <t>Расчётный целевой тариф за тонну (сценарий «База 250»)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -13905,92 +13979,98 @@
           <t>сум/т</t>
         </is>
       </c>
-      <c r="C2" s="12">
-        <f>ROUND('Расчёт'!F80/5000,0)*5000</f>
+      <c r="C2" s="10">
+        <f>'Расчёт'!F80</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Норма, ниже которой скорость ограничивает не подача, а предел скорости</t>
+          <t>ЕДИНЫЙ ТАРИФ за тонну внесённого удобрения (округление, один для всех удобрений)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>кг/га</t>
-        </is>
-      </c>
-      <c r="C3" s="16">
-        <f>10000/(swath_eff_m*speed_ms)/60*flow_kg_min</f>
+          <t>сум/т</t>
+        </is>
+      </c>
+      <c r="C3" s="12">
+        <f>unified_tariff_per_ton</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Минимальная цена гектара (тариф за тонну x эта норма)</t>
+          <t>Минимальный заказ за один выезд</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>сум/га</t>
-        </is>
-      </c>
-      <c r="C4" s="12">
-        <f>ROUND($C$2*$C$3/1000/5000,0)*5000</f>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="C4" s="14">
+        <f>min_order_t</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Минимальный заказ в деньгах</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>сум</t>
+        </is>
+      </c>
+      <c r="C5" s="12">
+        <f>unified_tariff_per_ton*min_order_t</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Норма, ниже которой гектар дешевле не становится (подача перестаёт ограничивать)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>кг/га</t>
+        </is>
+      </c>
+      <c r="C6" s="16">
+        <f>10000/(swath_eff_m*speed_ms)/60*flow_kg_min</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Норма, кг/га</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Цена для фермера, сум/га</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Цена для фермера, сум/га (справочно)</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>К тарифу опрыскивания, раз</t>
         </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>100</v>
-      </c>
-      <c r="B7" s="10">
-        <f>MAX($C$4,$C$2*A7/1000)</f>
-        <v/>
-      </c>
-      <c r="C7" s="9">
-        <f>B7/liquid_tariff_external</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>150</v>
-      </c>
-      <c r="B8" s="10">
-        <f>MAX($C$4,$C$2*A8/1000)</f>
-        <v/>
-      </c>
-      <c r="C8" s="9">
-        <f>B8/liquid_tariff_external</f>
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="B9" s="10">
-        <f>MAX($C$4,$C$2*A9/1000)</f>
+        <f>$C$3*A9/1000</f>
         <v/>
       </c>
       <c r="C9" s="9">
@@ -14000,10 +14080,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="B10" s="10">
-        <f>MAX($C$4,$C$2*A10/1000)</f>
+        <f>$C$3*A10/1000</f>
         <v/>
       </c>
       <c r="C10" s="9">
@@ -14013,10 +14093,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="B11" s="10">
-        <f>MAX($C$4,$C$2*A11/1000)</f>
+        <f>$C$3*A11/1000</f>
         <v/>
       </c>
       <c r="C11" s="9">
@@ -14026,10 +14106,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="B12" s="10">
-        <f>MAX($C$4,$C$2*A12/1000)</f>
+        <f>$C$3*A12/1000</f>
         <v/>
       </c>
       <c r="C12" s="9">
@@ -14037,10 +14117,36 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>300</v>
+      </c>
+      <c r="B13" s="10">
+        <f>$C$3*A13/1000</f>
+        <v/>
+      </c>
+      <c r="C13" s="9">
+        <f>B13/liquid_tariff_external</f>
+        <v/>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Почему «за тонну»: при нормах выше ~120 кг/га скорость над полем задаёт подача гранул (норматив: 8-11 км/ч при 7 м), и время над гектаром растёт пропорционально норме, как и число вылетов. Себестоимость гектара становится почти чисто пропорциональной килограммам -- строка C0 на листе «Расчёт» равна нулю, а ставка за тонну одинакова для 150, 250 и 400 кг/га. Минимум за гектар защищает выезд на лёгких нормах.</t>
+      <c r="A14" t="n">
+        <v>400</v>
+      </c>
+      <c r="B14" s="10">
+        <f>$C$3*A14/1000</f>
+        <v/>
+      </c>
+      <c r="C14" s="9">
+        <f>B14/liquid_tariff_external</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Почему один тариф «за тонну»: при нормах выше ~120 кг/га скорость над полем задаёт подача гранул (норматив: 8-11 км/ч при 7 м), и время над гектаром растёт пропорционально норме, как и число вылетов. Себестоимость гектара пропорциональна килограммам -- строка C0 на листе «Расчёт» равна нулю, а ставка за тонну одинакова для 150, 250 и 400 кг/га. Один тариф не даёт оператору выбирать «ступень» в отчёте; минимальный заказ отсекает мелкие работы. При нормах ниже 100 кг/га (семена) считать за гектар.</t>
         </is>
       </c>
     </row>

--- a/docs/research/drone-winter-spreading/model.xlsx
+++ b/docs/research/drone-winter-spreading/model.xlsx
@@ -13951,12 +13951,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14147,6 +14153,215 @@
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Почему один тариф «за тонну»: при нормах выше ~120 кг/га скорость над полем задаёт подача гранул (норматив: 8-11 км/ч при 7 м), и время над гектаром растёт пропорционально норме, как и число вылетов. Себестоимость гектара пропорциональна килограммам -- строка C0 на листе «Расчёт» равна нулю, а ставка за тонну одинакова для 150, 250 и 400 кг/га. Один тариф не даёт оператору выбирать «ступень» в отчёте; минимальный заказ отсекает мелкие работы. При нормах ниже 100 кг/га (семена) считать за гектар.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ЧТО ДАЁТ ТАРИФ: прибыль с тонны и за сезон (база 250 кг/га, 5 бортов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Тариф, сум/т</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость тонны</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Накладные 10 %</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>Прибыль с тонны</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>Маржа, %</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Цена гектара при 200 кг/га</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>К наземной альтернативе, раз</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>Прибыль за сезон до разовых</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>После разовых расходов</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="B20" s="10">
+        <f>'Расчёт'!F76*1000</f>
+        <v/>
+      </c>
+      <c r="C20" s="10">
+        <f>A20*overhead_pct</f>
+        <v/>
+      </c>
+      <c r="D20" s="10">
+        <f>A20-B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="13">
+        <f>D20/A20</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>A20*200/1000</f>
+        <v/>
+      </c>
+      <c r="G20" s="14">
+        <f>F20/ground_spread_cost_ha</f>
+        <v/>
+      </c>
+      <c r="H20" s="10">
+        <f>D20*'Расчёт'!F44*days_per_season*drones_in_winter</f>
+        <v/>
+      </c>
+      <c r="I20" s="10">
+        <f>H20-'Сезон'!D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="B21" s="10">
+        <f>'Расчёт'!F76*1000</f>
+        <v/>
+      </c>
+      <c r="C21" s="10">
+        <f>A21*overhead_pct</f>
+        <v/>
+      </c>
+      <c r="D21" s="10">
+        <f>A21-B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="13">
+        <f>D21/A21</f>
+        <v/>
+      </c>
+      <c r="F21" s="10">
+        <f>A21*200/1000</f>
+        <v/>
+      </c>
+      <c r="G21" s="14">
+        <f>F21/ground_spread_cost_ha</f>
+        <v/>
+      </c>
+      <c r="H21" s="10">
+        <f>D21*'Расчёт'!F44*days_per_season*drones_in_winter</f>
+        <v/>
+      </c>
+      <c r="I21" s="10">
+        <f>H21-'Сезон'!D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="B22" s="10">
+        <f>'Расчёт'!F76*1000</f>
+        <v/>
+      </c>
+      <c r="C22" s="10">
+        <f>A22*overhead_pct</f>
+        <v/>
+      </c>
+      <c r="D22" s="10">
+        <f>A22-B22-C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="13">
+        <f>D22/A22</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>A22*200/1000</f>
+        <v/>
+      </c>
+      <c r="G22" s="14">
+        <f>F22/ground_spread_cost_ha</f>
+        <v/>
+      </c>
+      <c r="H22" s="10">
+        <f>D22*'Расчёт'!F44*days_per_season*drones_in_winter</f>
+        <v/>
+      </c>
+      <c r="I22" s="10">
+        <f>H22-'Сезон'!D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="B23" s="10">
+        <f>'Расчёт'!F76*1000</f>
+        <v/>
+      </c>
+      <c r="C23" s="10">
+        <f>A23*overhead_pct</f>
+        <v/>
+      </c>
+      <c r="D23" s="10">
+        <f>A23-B23-C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="13">
+        <f>D23/A23</f>
+        <v/>
+      </c>
+      <c r="F23" s="10">
+        <f>A23*200/1000</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
+        <f>F23/ground_spread_cost_ha</f>
+        <v/>
+      </c>
+      <c r="H23" s="10">
+        <f>D23*'Расчёт'!F44*days_per_season*drones_in_winter</f>
+        <v/>
+      </c>
+      <c r="I23" s="10">
+        <f>H23-'Сезон'!D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Чтение: 1 778 сум/кг -- это расчётная цена, а не себестоимость; себестоимость 1 155. При 1 800 000 за тонну прибыль после накладных ~465 сум/кг (26 %). Поднятие тарифа увеличивает прибыль почти один к одному, но цена гектара уходит от наземной альтернативы (ДОГАДКА 100 000 сум/га) всё дальше.</t>
         </is>
       </c>
     </row>
